--- a/artfynd/A 17338-2026 artfynd.xlsx
+++ b/artfynd/A 17338-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103282665</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510642.4137103386</v>
+        <v>510642</v>
       </c>
       <c r="R2" t="n">
-        <v>6686952.042344491</v>
+        <v>6686952</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
